--- a/tests/fixtures/20_sales_report/20_sales_report_pattern-from-draft.xlsx
+++ b/tests/fixtures/20_sales_report/20_sales_report_pattern-from-draft.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>read.direction</t>
+          <t>pattern.version</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -441,34 +441,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>currency.sign</t>
+          <t>read.direction</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>€</t>
+          <t>LR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>config:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>col_product</t>
+          <t>currency.sign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Produkt</t>
+          <t>€</t>
         </is>
       </c>
     </row>
@@ -480,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>col_customer</t>
+          <t>col_product</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -490,7 +485,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kunde</t>
+          <t>Produkt</t>
         </is>
       </c>
     </row>
@@ -502,7 +497,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>col_q1</t>
+          <t>col_customer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -512,7 +507,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Qrtl 1</t>
+          <t>Kunde</t>
         </is>
       </c>
     </row>
@@ -524,7 +519,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>col_q2</t>
+          <t>col_q1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -534,7 +529,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Qrtl 2</t>
+          <t>Qrtl 1</t>
         </is>
       </c>
     </row>
@@ -546,7 +541,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>col_q3</t>
+          <t>col_q2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -556,7 +551,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Qrtl 3</t>
+          <t>Qrtl 2</t>
         </is>
       </c>
     </row>
@@ -568,7 +563,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>col_q4</t>
+          <t>col_q3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -578,19 +573,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Qrtl 4</t>
+          <t>Qrtl 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>line.product</t>
+          <t>col_q4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -600,7 +595,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>Qrtl 4</t>
         </is>
       </c>
     </row>
@@ -612,7 +607,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>line.customer</t>
+          <t>line.product</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -622,7 +617,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[A-Z]+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -634,17 +629,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>line.q1</t>
+          <t>line.customer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>[A-Z]+</t>
         </is>
       </c>
     </row>
@@ -656,7 +651,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>line.q2</t>
+          <t>line.q1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -678,7 +673,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>line.q3</t>
+          <t>line.q2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -700,7 +695,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>line.q4</t>
+          <t>line.q3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -717,95 +712,115 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>line.q4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>START:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>table:*</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>col_customer</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>col_q1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>col_q2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>col_q3</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>col_q4</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>line.product</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>line.customer</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>line.q1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>line.q2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>line.q3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>line.q4</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
